--- a/cases/Fault_Cases/ieee39_fault.xlsx
+++ b/cases/Fault_Cases/ieee39_fault.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aali27/Work/repos/emt_simulator_basic/cases/Fault_Cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8483E26D-31BA-6945-9430-1CFD4B8AA18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F84319D-CCF9-6F48-A288-896C3B941C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="19200" windowHeight="17700" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -11052,7 +11052,7 @@
         <v>273</v>
       </c>
       <c r="E2" s="5">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -11061,10 +11061,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H2" s="6">
-        <v>10000000000</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I2" s="6">
-        <v>10000000000</v>
+        <v>1E-4</v>
       </c>
     </row>
   </sheetData>
